--- a/tests/testdata/excel/ファイル名/コピー.xls_old.xlsx
+++ b/tests/testdata/excel/ファイル名/コピー.xls_old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45C921F2-0690-43B2-8058-3AE7B5E0D980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E19EBFDC-5424-414A-98C0-CBBB3AA802A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="10515" xr2:uid="{FF7F2B0D-632D-4351-BCFD-BFD1031F8DD1}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{F6982F2A-E2E7-4DDE-A1AD-EA7ABCA8846D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76D1C661-E713-4338-8913-892123C8945F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322B6A53-96FE-4DFA-90FB-9D0C7F161191}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>

--- a/tests/testdata/excel/ファイル名/コピー.xls_old.xlsx
+++ b/tests/testdata/excel/ファイル名/コピー.xls_old.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E19EBFDC-5424-414A-98C0-CBBB3AA802A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8C8EB2D-E6E0-4833-A3FF-F4182C9D578F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{F6982F2A-E2E7-4DDE-A1AD-EA7ABCA8846D}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{AE9FA1AB-F9C7-4B6A-817B-4338CC1763EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322B6A53-96FE-4DFA-90FB-9D0C7F161191}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91161341-74E4-4A12-BC88-77C0CAEC83FB}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
